--- a/resources/print-on-demand/files/pod-basics-price-floor.xlsx
+++ b/resources/print-on-demand/files/pod-basics-price-floor.xlsx
@@ -17,10 +17,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="£#,##0.00"/>
+    <numFmt numFmtId="164" formatCode="$#,##0.00"/>
     <numFmt numFmtId="165" formatCode="0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -61,11 +61,6 @@
       <color rgb="000C2733"/>
       <sz val="12"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="005A5A5A"/>
-    </font>
-    <font/>
   </fonts>
   <fills count="3">
     <fill>
@@ -92,7 +87,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -110,8 +105,6 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -477,7 +470,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -498,7 +491,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -522,11 +514,11 @@
     <row r="6">
       <c r="A6" s="3" t="inlineStr">
         <is>
-          <t>Fixed fees per sale (listing renewal + fixed card processing)</t>
+          <t>Fixed fees per sale (Etsy US: $0.20 listing + $0.25 processing)</t>
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="7">
@@ -552,14 +544,13 @@
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>Platform fee %  (10 US · ~12 UK Etsy+VAT)</t>
+          <t>Platform fee %  (Etsy ~10 · ~12 with Offsite Ads)</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
         <v>10</v>
       </c>
     </row>
-    <row r="10"/>
     <row r="11">
       <c r="A11" s="6" t="inlineStr">
         <is>
@@ -571,7 +562,6 @@
         <v/>
       </c>
     </row>
-    <row r="12"/>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -583,7 +573,6 @@
         <v/>
       </c>
     </row>
-    <row r="14"/>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
@@ -605,7 +594,6 @@
         </is>
       </c>
     </row>
-    <row r="18"/>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
@@ -619,10 +607,6 @@
           <t>ePORTS — your ecom source. eports.global.</t>
         </is>
       </c>
-    </row>
-    <row r="21"/>
-    <row r="22">
-      <c r="A22" s="10" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/resources/print-on-demand/files/pod-basics-price-floor.xlsx
+++ b/resources/print-on-demand/files/pod-basics-price-floor.xlsx
@@ -604,7 +604,7 @@
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ePORTS — your ecom source. eports.global.</t>
+          <t>ePORTS — your ecom source (eports.global)</t>
         </is>
       </c>
     </row>
